--- a/Maret-2026.xlsx
+++ b/Maret-2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DBA07ED-A8D9-49E5-9AD6-89A272699E0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E020B491-7D4C-40BA-8678-2D86516C47BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Agent" sheetId="1" r:id="rId1"/>
@@ -165,7 +165,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -176,26 +176,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
       <top/>
       <bottom style="thin">
         <color indexed="64"/>
@@ -221,49 +201,55 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -600,16 +586,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="8">
-        <v>356</v>
+        <v>425</v>
       </c>
       <c r="C2" s="8">
-        <v>529</v>
+        <v>649</v>
       </c>
       <c r="D2" s="7">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E2" s="9">
-        <v>2.2400000000000002</v>
+        <v>2.0499999999999998</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -617,16 +603,16 @@
         <v>6</v>
       </c>
       <c r="B3" s="8">
-        <v>316</v>
+        <v>413</v>
       </c>
       <c r="C3" s="8">
-        <v>564</v>
+        <v>731</v>
       </c>
       <c r="D3" s="7">
         <v>25</v>
       </c>
       <c r="E3" s="9">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -634,16 +620,16 @@
         <v>7</v>
       </c>
       <c r="B4" s="8">
-        <v>309</v>
+        <v>421</v>
       </c>
       <c r="C4" s="8">
-        <v>493</v>
+        <v>671</v>
       </c>
       <c r="D4" s="7">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="E4" s="9">
-        <v>2</v>
+        <v>2.4500000000000002</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -651,16 +637,16 @@
         <v>8</v>
       </c>
       <c r="B5" s="8">
-        <v>330</v>
+        <v>403</v>
       </c>
       <c r="C5" s="8">
-        <v>715</v>
+        <v>814</v>
       </c>
       <c r="D5" s="7">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="E5" s="9">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -668,16 +654,16 @@
         <v>9</v>
       </c>
       <c r="B6" s="8">
-        <v>286</v>
+        <v>356</v>
       </c>
       <c r="C6" s="8">
-        <v>894</v>
+        <v>1107</v>
       </c>
       <c r="D6" s="7">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E6" s="9">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -685,16 +671,16 @@
         <v>10</v>
       </c>
       <c r="B7" s="8">
-        <v>286</v>
+        <v>361</v>
       </c>
       <c r="C7" s="8">
-        <v>964</v>
+        <v>1112</v>
       </c>
       <c r="D7" s="7">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="E7" s="9">
-        <v>1.82</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -702,16 +688,16 @@
         <v>11</v>
       </c>
       <c r="B8" s="8">
-        <v>433</v>
+        <v>507</v>
       </c>
       <c r="C8" s="8">
-        <v>912</v>
+        <v>1099</v>
       </c>
       <c r="D8" s="7">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="E8" s="9">
-        <v>3.47</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -719,16 +705,16 @@
         <v>12</v>
       </c>
       <c r="B9" s="8">
-        <v>223</v>
+        <v>260</v>
       </c>
       <c r="C9" s="8">
-        <v>988</v>
+        <v>1178</v>
       </c>
       <c r="D9" s="7">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="E9" s="9">
-        <v>3.41</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -736,16 +722,16 @@
         <v>13</v>
       </c>
       <c r="B10" s="8">
-        <v>496</v>
+        <v>562</v>
       </c>
       <c r="C10" s="8">
-        <v>757</v>
+        <v>853</v>
       </c>
       <c r="D10" s="7">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="E10" s="9">
-        <v>3.24</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -753,16 +739,16 @@
         <v>14</v>
       </c>
       <c r="B11" s="8">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="C11" s="8">
-        <v>961</v>
+        <v>1000</v>
       </c>
       <c r="D11" s="7">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E11" s="9">
-        <v>2.1800000000000002</v>
+        <v>2.0499999999999998</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -770,16 +756,16 @@
         <v>15</v>
       </c>
       <c r="B12" s="8">
-        <v>383</v>
+        <v>435</v>
       </c>
       <c r="C12" s="8">
-        <v>825</v>
+        <v>940</v>
       </c>
       <c r="D12" s="7">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="E12" s="9">
-        <v>2.29</v>
+        <v>2.2999999999999998</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -793,10 +779,10 @@
         <v>1003</v>
       </c>
       <c r="D13" s="7">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E13" s="9">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -810,10 +796,10 @@
         <v>911</v>
       </c>
       <c r="D14" s="7">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E14" s="9">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -821,16 +807,16 @@
         <v>18</v>
       </c>
       <c r="B15" s="8">
-        <v>542</v>
+        <v>651</v>
       </c>
       <c r="C15" s="8">
-        <v>1032</v>
+        <v>1108</v>
       </c>
       <c r="D15" s="7">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="E15" s="9">
-        <v>4.29</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -844,7 +830,7 @@
         <v>878</v>
       </c>
       <c r="D16" s="7">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E16" s="9">
         <v>1.35</v>
@@ -855,16 +841,16 @@
         <v>20</v>
       </c>
       <c r="B17" s="8">
-        <v>245</v>
+        <v>290</v>
       </c>
       <c r="C17" s="8">
-        <v>1100</v>
+        <v>1272</v>
       </c>
       <c r="D17" s="7">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="E17" s="9">
-        <v>1.35</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -872,16 +858,16 @@
         <v>21</v>
       </c>
       <c r="B18" s="8">
-        <v>320</v>
+        <v>363</v>
       </c>
       <c r="C18" s="8">
-        <v>696</v>
+        <v>809</v>
       </c>
       <c r="D18" s="7">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E18" s="9">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -889,16 +875,16 @@
         <v>23</v>
       </c>
       <c r="B19" s="12">
-        <v>5419</v>
+        <v>6347</v>
       </c>
       <c r="C19" s="12">
-        <v>14222</v>
+        <v>16135</v>
       </c>
       <c r="D19" s="11">
-        <v>665</v>
+        <v>816</v>
       </c>
       <c r="E19" s="13">
-        <v>2.2999999999999998</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -974,13 +960,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Z34"/>
+  <dimension ref="A1:AE34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="30" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -1056,12 +1047,27 @@
       <c r="Y1" s="17">
         <v>46107</v>
       </c>
-      <c r="Z1" s="18" t="s">
+      <c r="Z1" s="17">
+        <v>46108</v>
+      </c>
+      <c r="AA1" s="17">
+        <v>46109</v>
+      </c>
+      <c r="AB1" s="17">
+        <v>46110</v>
+      </c>
+      <c r="AC1" s="17">
+        <v>46111</v>
+      </c>
+      <c r="AD1" s="17">
+        <v>46112</v>
+      </c>
+      <c r="AE1" s="17" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A2" s="18" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="2">
@@ -1136,12 +1142,27 @@
       <c r="Y2" s="2">
         <v>0</v>
       </c>
-      <c r="Z2" s="20">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="Z2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="2">
+        <v>33</v>
+      </c>
+      <c r="AB2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="2">
+        <v>42</v>
+      </c>
+      <c r="AD2" s="2">
+        <v>114</v>
+      </c>
+      <c r="AE2" s="2">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A3" s="18" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2">
@@ -1216,12 +1237,27 @@
       <c r="Y3" s="2">
         <v>0</v>
       </c>
-      <c r="Z3" s="20">
-        <v>880</v>
-      </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
+      <c r="Z3" s="2">
+        <v>49</v>
+      </c>
+      <c r="AA3" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="2">
+        <v>29</v>
+      </c>
+      <c r="AC3" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD3" s="2">
+        <v>104</v>
+      </c>
+      <c r="AE3" s="2">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A4" s="18" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="2">
@@ -1296,12 +1332,27 @@
       <c r="Y4" s="2">
         <v>107</v>
       </c>
-      <c r="Z4" s="20">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
+      <c r="Z4" s="2">
+        <v>55</v>
+      </c>
+      <c r="AA4" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="2">
+        <v>103</v>
+      </c>
+      <c r="AD4" s="2">
+        <v>110</v>
+      </c>
+      <c r="AE4" s="2">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A5" s="18" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="2">
@@ -1376,12 +1427,27 @@
       <c r="Y5" s="2">
         <v>118</v>
       </c>
-      <c r="Z5" s="20">
-        <v>1043</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
+      <c r="Z5" s="2">
+        <v>39</v>
+      </c>
+      <c r="AA5" s="2">
+        <v>25</v>
+      </c>
+      <c r="AB5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="2">
+        <v>108</v>
+      </c>
+      <c r="AD5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="2">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A6" s="18" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="2">
@@ -1456,12 +1522,27 @@
       <c r="Y6" s="2">
         <v>118</v>
       </c>
-      <c r="Z6" s="20">
-        <v>1179</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
+      <c r="Z6" s="2">
+        <v>46</v>
+      </c>
+      <c r="AA6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="2">
+        <v>116</v>
+      </c>
+      <c r="AD6" s="2">
+        <v>121</v>
+      </c>
+      <c r="AE6" s="2">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A7" s="18" t="s">
         <v>10</v>
       </c>
       <c r="B7" s="2">
@@ -1536,12 +1617,27 @@
       <c r="Y7" s="2">
         <v>0</v>
       </c>
-      <c r="Z7" s="20">
-        <v>1248</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
+      <c r="Z7" s="2">
+        <v>37</v>
+      </c>
+      <c r="AA7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD7" s="2">
+        <v>112</v>
+      </c>
+      <c r="AE7" s="2">
+        <v>1471</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A8" s="18" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="2">
@@ -1616,12 +1712,27 @@
       <c r="Y8" s="2">
         <v>109</v>
       </c>
-      <c r="Z8" s="20">
-        <v>1343</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
+      <c r="Z8" s="2">
+        <v>43</v>
+      </c>
+      <c r="AA8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="2">
+        <v>118</v>
+      </c>
+      <c r="AD8" s="2">
+        <v>100</v>
+      </c>
+      <c r="AE8" s="2">
+        <v>1604</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A9" s="18" t="s">
         <v>12</v>
       </c>
       <c r="B9" s="2">
@@ -1696,12 +1807,27 @@
       <c r="Y9" s="2">
         <v>106</v>
       </c>
-      <c r="Z9" s="20">
-        <v>1210</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
+      <c r="Z9" s="2">
+        <v>41</v>
+      </c>
+      <c r="AA9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="2">
+        <v>86</v>
+      </c>
+      <c r="AD9" s="2">
+        <v>100</v>
+      </c>
+      <c r="AE9" s="2">
+        <v>1437</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A10" s="18" t="s">
         <v>13</v>
       </c>
       <c r="B10" s="2">
@@ -1776,12 +1902,27 @@
       <c r="Y10" s="2">
         <v>108</v>
       </c>
-      <c r="Z10" s="20">
-        <v>1251</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
+      <c r="Z10" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="2">
+        <v>16</v>
+      </c>
+      <c r="AC10" s="2">
+        <v>45</v>
+      </c>
+      <c r="AD10" s="2">
+        <v>101</v>
+      </c>
+      <c r="AE10" s="2">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A11" s="18" t="s">
         <v>14</v>
       </c>
       <c r="B11" s="2">
@@ -1856,12 +1997,27 @@
       <c r="Y11" s="2">
         <v>104</v>
       </c>
-      <c r="Z11" s="20">
-        <v>1251</v>
-      </c>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
+      <c r="Z11" s="2">
+        <v>45</v>
+      </c>
+      <c r="AA11" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="2">
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A12" s="18" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="2">
@@ -1936,12 +2092,27 @@
       <c r="Y12" s="2">
         <v>0</v>
       </c>
-      <c r="Z12" s="20">
-        <v>1207</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
+      <c r="Z12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="2">
+        <v>56</v>
+      </c>
+      <c r="AD12" s="2">
+        <v>111</v>
+      </c>
+      <c r="AE12" s="2">
+        <v>1374</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A13" s="18" t="s">
         <v>16</v>
       </c>
       <c r="B13" s="2">
@@ -2016,12 +2187,27 @@
       <c r="Y13" s="2">
         <v>96</v>
       </c>
-      <c r="Z13" s="20">
+      <c r="Z13" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="2">
         <v>1225</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A14" s="19" t="s">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A14" s="18" t="s">
         <v>17</v>
       </c>
       <c r="B14" s="2">
@@ -2096,12 +2282,27 @@
       <c r="Y14" s="2">
         <v>99</v>
       </c>
-      <c r="Z14" s="20">
+      <c r="Z14" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="2">
         <v>1076</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A15" s="18" t="s">
         <v>18</v>
       </c>
       <c r="B15" s="2">
@@ -2176,12 +2377,27 @@
       <c r="Y15" s="2">
         <v>99</v>
       </c>
-      <c r="Z15" s="20">
-        <v>1564</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
+      <c r="Z15" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB15" s="2">
+        <v>47</v>
+      </c>
+      <c r="AC15" s="2">
+        <v>3</v>
+      </c>
+      <c r="AD15" s="2">
+        <v>110</v>
+      </c>
+      <c r="AE15" s="2">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A16" s="18" t="s">
         <v>19</v>
       </c>
       <c r="B16" s="2">
@@ -2256,12 +2472,27 @@
       <c r="Y16" s="2">
         <v>0</v>
       </c>
-      <c r="Z16" s="20">
+      <c r="Z16" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="2">
         <v>1089</v>
       </c>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A17" s="19" t="s">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A17" s="18" t="s">
         <v>20</v>
       </c>
       <c r="B17" s="2">
@@ -2336,12 +2567,27 @@
       <c r="Y17" s="2">
         <v>105</v>
       </c>
-      <c r="Z17" s="20">
-        <v>1344</v>
-      </c>
-    </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A18" s="21" t="s">
+      <c r="Z17" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA17" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="2">
+        <v>93</v>
+      </c>
+      <c r="AD17" s="2">
+        <v>105</v>
+      </c>
+      <c r="AE17" s="2">
+        <v>1561</v>
+      </c>
+    </row>
+    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A18" s="19" t="s">
         <v>21</v>
       </c>
       <c r="B18" s="3">
@@ -2416,12 +2662,27 @@
       <c r="Y18" s="3">
         <v>0</v>
       </c>
-      <c r="Z18" s="22">
-        <v>1011</v>
-      </c>
-    </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A19" s="23" t="s">
+      <c r="Z18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="3">
+        <v>52</v>
+      </c>
+      <c r="AD18" s="3">
+        <v>104</v>
+      </c>
+      <c r="AE18" s="3">
+        <v>1167</v>
+      </c>
+    </row>
+    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A19" s="20" t="s">
         <v>23</v>
       </c>
       <c r="B19" s="4">
@@ -2496,47 +2757,62 @@
       <c r="Y19" s="4">
         <v>1169</v>
       </c>
-      <c r="Z19" s="24">
-        <v>19604</v>
-      </c>
-    </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="Z19" s="4">
+        <v>374</v>
+      </c>
+      <c r="AA19" s="4">
+        <v>103</v>
+      </c>
+      <c r="AB19" s="4">
+        <v>92</v>
+      </c>
+      <c r="AC19" s="4">
+        <v>978</v>
+      </c>
+      <c r="AD19" s="4">
+        <v>1292</v>
+      </c>
+      <c r="AE19" s="4">
+        <v>22443</v>
+      </c>
+    </row>
+    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A20" s="15"/>
     </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A21" s="15"/>
     </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A22" s="15"/>
     </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A23" s="15"/>
     </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A24" s="15"/>
     </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A25" s="15"/>
     </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A26" s="15"/>
     </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A27" s="15"/>
     </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A28" s="15"/>
     </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A29" s="15"/>
     </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A30" s="15"/>
     </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A31" s="15"/>
     </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A32" s="15"/>
     </row>
     <row r="33" spans="3:3" x14ac:dyDescent="0.25">
@@ -2546,8 +2822,8 @@
       <c r="C34" s="14"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:Y18">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
+  <conditionalFormatting sqref="B2:AD18">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
       <formula>99</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2567,7 +2843,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>2.2999999999999998</v>
+        <v>2.4</v>
       </c>
     </row>
   </sheetData>
